--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00736-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00736-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{36B72786-589F-43CA-B794-64FA00043865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE34E8A9-B0BC-4C4B-97A5-9A6302C061D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{ED59E25F-05D8-4BDF-B915-6C28F853F36E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{ED5F1565-5CB8-43F7-B5FE-BF814C366E1F}"/>
   </bookViews>
   <sheets>
     <sheet name="00736-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1537,20 +1537,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E10AF554-7CF4-4F46-87CB-35A1EC207CCE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CBE02D9-E02D-4B95-A607-65B2CD1FBAD2}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1578,7 +1578,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1608,7 +1608,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1704,7 +1704,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>2.0499999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1784,7 +1784,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1894,7 +1894,7 @@
         <v>2.02</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2006,7 +2006,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="51">
         <v>2024</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>27</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>0.55000000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>27</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="49">
         <v>2023</v>
       </c>
@@ -2226,7 +2226,7 @@
         <v>1.56</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>27</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>0.63</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>27</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>0.93</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="51">
         <v>2022</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>27</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>27</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="49">
         <v>2021</v>
       </c>
@@ -2558,7 +2558,7 @@
         <v>1.7</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2614,7 +2614,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2670,7 +2670,7 @@
         <v>1.06</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2020</v>
       </c>
@@ -2724,7 +2724,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="49">
         <v>2019</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>1.95</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
         <v>27</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
         <v>27</v>
       </c>
@@ -2946,7 +2946,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="51" t="s">
         <v>50</v>
       </c>
